--- a/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/confusion_matrix_unified.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/confusion_matrix_unified.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Part 1: Training Resubstitution — Core (n=35) + Peripheral (n=10)</t>
+          <t>Part 1: Training Resubstitution — Core (n=25) + Peripheral (n=23)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -510,10 +510,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -548,7 +548,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Part 2: 5-Fold x 10 Cross-Validation — Core (n=35) + Peripheral (n=10)</t>
+          <t>Part 2: 5-Fold x 10 Cross-Validation — Core (n=25) + Peripheral (n=23)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -586,16 +586,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
+        <v>76</v>
+      </c>
+      <c r="E10" t="n">
         <v>29</v>
-      </c>
-      <c r="E10" t="n">
-        <v>121</v>
       </c>
     </row>
     <row r="11">
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -643,16 +643,16 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>57</v>
+      </c>
+      <c r="C13" t="n">
+        <v>288</v>
+      </c>
+      <c r="D13" t="n">
+        <v>149</v>
+      </c>
+      <c r="E13" t="n">
         <v>43</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>203</v>
-      </c>
-      <c r="E13" t="n">
-        <v>247</v>
       </c>
     </row>
     <row r="14">
@@ -665,7 +665,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Part 3: Held-out Prediction — Uncertain (n=5)</t>
+          <t>Part 3: Held-out Prediction — Uncertain (n=2)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -744,10 +744,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>

--- a/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/confusion_matrix_unified.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelC_Weighted/tables/confusion_matrix_unified.xlsx
@@ -431,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Part 1: Training Resubstitution — Core (n=25) + Peripheral (n=23)</t>
+          <t>Part 1: Training Resubstitution — Core (n=42) + Peripheral (n=6)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -548,7 +548,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Part 2: 5-Fold x 10 Cross-Validation — Core (n=25) + Peripheral (n=23)</t>
+          <t>Part 2: 5-Fold x 10 Cross-Validation — Core (n=42) + Peripheral (n=6)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -586,16 +586,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -608,13 +608,13 @@
         <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
         <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -643,16 +643,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C13" t="n">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="D13" t="n">
         <v>149</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
